--- a/abtesting_instructions/instructions_mvt_2.xlsx
+++ b/abtesting_instructions/instructions_mvt_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\AB-testing-app\abtesting_instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36EED8E-3B5E-4FD6-A3F9-FE69C41B2EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0A0CCA-C55B-41EF-B1BC-40CFAD463508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="99945" yWindow="4185" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37620" yWindow="1245" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Test Name</t>
   </si>
@@ -36,7 +36,34 @@
     <t>Normal office lighting --- Eye blinking: slow and fast</t>
   </si>
   <si>
-    <t>Test Condition</t>
+    <t>Test Condition 1</t>
+  </si>
+  <si>
+    <t>Normal office lighting --- Stationary viewing</t>
+  </si>
+  <si>
+    <t>Test Condition 2</t>
+  </si>
+  <si>
+    <t>Normal office lighting --- Active movement: Slow+fast left/right, yaw, pitch, roll, etc.</t>
+  </si>
+  <si>
+    <t>Test Condition 3</t>
+  </si>
+  <si>
+    <t>Test Condition 5</t>
+  </si>
+  <si>
+    <t>Low lighting  --- Stationary viewing</t>
+  </si>
+  <si>
+    <t>Low lighting --- Active movement: Slow+fast left/right, yaw, pitch, roll, etc.</t>
+  </si>
+  <si>
+    <t>Test Condition 6</t>
+  </si>
+  <si>
+    <t>Low lighting --- Eye blinking: slow anf fast</t>
   </si>
 </sst>
 </file>
@@ -360,14 +387,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -375,12 +402,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/abtesting_instructions/instructions_mvt_2.xlsx
+++ b/abtesting_instructions/instructions_mvt_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\AB-testing-app\abtesting_instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0A0CCA-C55B-41EF-B1BC-40CFAD463508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CCCE27-109B-453B-A044-30B28ACAA4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="1245" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32925" yWindow="2610" windowWidth="28800" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Test Name</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Low lighting --- Eye blinking: slow anf fast</t>
+  </si>
+  <si>
+    <t>Test Condition 4</t>
   </si>
 </sst>
 </file>
@@ -428,7 +431,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>

--- a/abtesting_instructions/instructions_mvt_2.xlsx
+++ b/abtesting_instructions/instructions_mvt_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\AB-testing-app\abtesting_instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CCCE27-109B-453B-A044-30B28ACAA4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08155C1-0CC2-49EB-B2EA-8BE2777681B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32925" yWindow="2610" windowWidth="28800" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,10 +63,10 @@
     <t>Test Condition 6</t>
   </si>
   <si>
-    <t>Low lighting --- Eye blinking: slow anf fast</t>
-  </si>
-  <si>
     <t>Test Condition 4</t>
+  </si>
+  <si>
+    <t>Low lighting --- Eye blinking: slow and fast</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -450,7 +450,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
